--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="110">
   <si>
     <t>Result</t>
   </si>
@@ -537,6 +537,45 @@
   </si>
   <si>
     <t>Fri Jul 24 18:00:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:03:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:04:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:05:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:06:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:06:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:13:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:13:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:14:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:14:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:15:33 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1016,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1121,7 +1160,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>21</v>
@@ -1266,7 +1305,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1409,7 +1448,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1552,7 +1591,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1695,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1839,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1982,7 +2021,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2125,7 +2164,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2268,7 +2307,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
